--- a/utils/monday_sprint_sprint_2025-15.xlsx
+++ b/utils/monday_sprint_sprint_2025-15.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="273">
   <si>
     <t>Ticket</t>
   </si>
@@ -153,7 +153,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Semana 4</t>
@@ -288,7 +288,7 @@
     <t>17/06/2025</t>
   </si>
   <si>
-    <t>02/03/2026</t>
+    <t>25/02/2026</t>
   </si>
   <si>
     <t>Semana 3</t>
@@ -381,7 +381,7 @@
     <t>30/05/2025</t>
   </si>
   <si>
-    <t>14/03/2026</t>
+    <t>09/03/2026</t>
   </si>
   <si>
     <t>32310</t>
@@ -430,6 +430,9 @@
   </si>
   <si>
     <t>31/01/2025</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
   </si>
   <si>
     <t>Janeiro</t>
@@ -3141,7 +3144,7 @@
         <v>138</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>96</v>
@@ -3150,12 +3153,12 @@
         <v>56</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -3167,10 +3170,10 @@
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>19</v>
@@ -3199,7 +3202,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
@@ -3211,10 +3214,10 @@
         <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>19</v>
@@ -3243,7 +3246,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -3255,10 +3258,10 @@
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>19</v>
@@ -3287,7 +3290,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3299,10 +3302,10 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>19</v>
@@ -3343,10 +3346,10 @@
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>19</v>
@@ -3387,10 +3390,10 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>19</v>
@@ -3419,7 +3422,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3431,10 +3434,10 @@
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>19</v>
@@ -3463,7 +3466,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3475,10 +3478,10 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>19</v>
@@ -3519,10 +3522,10 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>19</v>
@@ -3551,7 +3554,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3563,10 +3566,10 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>19</v>
@@ -3595,7 +3598,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3607,10 +3610,10 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>19</v>
@@ -3651,10 +3654,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>19</v>
@@ -3683,7 +3686,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3695,10 +3698,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>19</v>
@@ -3727,7 +3730,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -3739,10 +3742,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>19</v>
@@ -3771,7 +3774,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -3783,10 +3786,10 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>19</v>
@@ -3815,7 +3818,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -3827,22 +3830,22 @@
         <v>40</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>44</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>91</v>
@@ -3859,7 +3862,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -3871,10 +3874,10 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>19</v>
@@ -3903,7 +3906,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -3915,22 +3918,22 @@
         <v>40</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>44</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>91</v>
@@ -3947,7 +3950,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -3959,10 +3962,10 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>19</v>
@@ -3991,7 +3994,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -4003,10 +4006,10 @@
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>19</v>
@@ -4035,7 +4038,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -4047,10 +4050,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>19</v>
@@ -4079,7 +4082,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -4091,10 +4094,10 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>19</v>
@@ -4123,7 +4126,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -4135,25 +4138,25 @@
         <v>40</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>44</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>20</v>
@@ -4167,7 +4170,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4179,10 +4182,10 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>25</v>
@@ -4211,7 +4214,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4223,10 +4226,10 @@
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>19</v>
@@ -4255,7 +4258,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4267,10 +4270,10 @@
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>19</v>
@@ -4311,10 +4314,10 @@
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>19</v>
@@ -4355,10 +4358,10 @@
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>19</v>
@@ -4387,7 +4390,7 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4399,10 +4402,10 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>19</v>
@@ -4431,7 +4434,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -4443,10 +4446,10 @@
         <v>40</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>19</v>
@@ -4458,7 +4461,7 @@
         <v>44</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>17</v>
@@ -4475,7 +4478,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4487,10 +4490,10 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>19</v>
@@ -4519,7 +4522,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -4531,10 +4534,10 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>25</v>
@@ -4575,10 +4578,10 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>19</v>
@@ -4607,7 +4610,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -4619,10 +4622,10 @@
         <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>19</v>
@@ -4651,7 +4654,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -4663,10 +4666,10 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>19</v>
@@ -4695,7 +4698,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
@@ -4707,10 +4710,10 @@
         <v>40</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>19</v>
@@ -4725,7 +4728,7 @@
         <v>138</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>28</v>
@@ -4734,12 +4737,12 @@
         <v>56</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -4751,10 +4754,10 @@
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>25</v>
@@ -4783,7 +4786,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -4795,10 +4798,10 @@
         <v>17</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>19</v>
@@ -4827,7 +4830,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -4839,10 +4842,10 @@
         <v>17</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>25</v>
@@ -4871,7 +4874,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
@@ -4883,10 +4886,10 @@
         <v>40</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>19</v>
@@ -4898,10 +4901,10 @@
         <v>70</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>36</v>
@@ -4915,7 +4918,7 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
@@ -4927,10 +4930,10 @@
         <v>17</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>19</v>
@@ -4959,7 +4962,7 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
@@ -4971,10 +4974,10 @@
         <v>17</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>19</v>
@@ -5003,7 +5006,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
@@ -5015,10 +5018,10 @@
         <v>17</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>19</v>
@@ -5047,7 +5050,7 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
@@ -5059,10 +5062,10 @@
         <v>17</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>19</v>
@@ -5091,7 +5094,7 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
@@ -5103,10 +5106,10 @@
         <v>17</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>25</v>
@@ -5135,7 +5138,7 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>15</v>
@@ -5147,10 +5150,10 @@
         <v>17</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>19</v>
@@ -5179,7 +5182,7 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>15</v>
@@ -5191,10 +5194,10 @@
         <v>17</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>19</v>
@@ -5223,7 +5226,7 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>15</v>
@@ -5235,10 +5238,10 @@
         <v>17</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>19</v>
@@ -5267,7 +5270,7 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>15</v>
@@ -5279,10 +5282,10 @@
         <v>17</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>25</v>
@@ -5311,7 +5314,7 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>15</v>
@@ -5323,25 +5326,25 @@
         <v>40</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>44</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>72</v>
@@ -5355,7 +5358,7 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>15</v>
@@ -5367,25 +5370,25 @@
         <v>40</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>44</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>20</v>
@@ -5399,7 +5402,7 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>15</v>
@@ -5411,10 +5414,10 @@
         <v>17</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>19</v>
@@ -5443,7 +5446,7 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>15</v>
@@ -5455,25 +5458,25 @@
         <v>40</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>44</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>20</v>
@@ -5487,7 +5490,7 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>15</v>
@@ -5499,25 +5502,25 @@
         <v>40</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>44</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="L97" s="2" t="s">
         <v>72</v>
@@ -5542,23 +5545,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5566,16 +5569,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5594,7 +5597,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5615,7 +5618,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5646,12 +5649,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B2">
         <v>96</v>
@@ -5675,25 +5678,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5710,13 +5713,13 @@
         <v>77</v>
       </c>
       <c r="G10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5731,7 +5734,7 @@
         <v>29</v>
       </c>
       <c r="Q10">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -5748,7 +5751,7 @@
         <v>17</v>
       </c>
       <c r="J11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K11">
         <v>96</v>
@@ -5763,7 +5766,7 @@
         <v>21</v>
       </c>
       <c r="Q11">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -5789,7 +5792,7 @@
         <v>92</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
@@ -5800,7 +5803,7 @@
         <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -5815,12 +5818,12 @@
         <v>47</v>
       </c>
       <c r="Q13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -5848,7 +5851,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5856,7 +5859,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5864,7 +5867,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -5875,7 +5878,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5889,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>41</v>
@@ -5903,7 +5906,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>49</v>
@@ -5917,7 +5920,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>59</v>
@@ -5931,7 +5934,7 @@
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>60</v>
@@ -5945,7 +5948,7 @@
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>136</v>
@@ -5953,55 +5956,55 @@
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>183</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>240</v>
@@ -6009,16 +6012,16 @@
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2025-15.xlsx
+++ b/utils/monday_sprint_sprint_2025-15.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="294">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>32756</t>
+    <t>9572189617</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>11/07/2025</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>15/07/2025</t>
   </si>
   <si>
     <t>Feito</t>
@@ -117,7 +117,7 @@
     <t>14/07/2025</t>
   </si>
   <si>
-    <t>31270</t>
+    <t>9279941747</t>
   </si>
   <si>
     <t>MELHORIAS FLUXO 109 REVISÕES</t>
@@ -126,55 +126,67 @@
     <t>02/06/2025</t>
   </si>
   <si>
+    <t>13/07/2025</t>
+  </si>
+  <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
     <t>Semana 1</t>
   </si>
   <si>
     <t>Junho</t>
   </si>
   <si>
-    <t>32734</t>
+    <t>9572283663</t>
   </si>
   <si>
     <t>APONTAMENTO ELETRONICO JATO DIRIGIDO</t>
   </si>
   <si>
-    <t>32743</t>
+    <t>24/07/2025</t>
+  </si>
+  <si>
+    <t>9572201682</t>
   </si>
   <si>
     <t>Padronização painel de produção</t>
   </si>
   <si>
-    <t>28583</t>
+    <t>9581432350</t>
   </si>
   <si>
     <t>Compara Carteira UPR - Erro</t>
   </si>
   <si>
+    <t>27/07/2025</t>
+  </si>
+  <si>
     <t>Fazendo</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>9581038075</t>
   </si>
   <si>
     <t>Integração de faturamentos com eventos</t>
   </si>
   <si>
-    <t>19909</t>
+    <t>9572710571</t>
   </si>
   <si>
     <t>Planilha - Registro Pintura</t>
   </si>
   <si>
+    <t>9572705481</t>
+  </si>
+  <si>
     <t>Tela de ajustes - Registro Pintura</t>
   </si>
   <si>
-    <t>32512</t>
+    <t>17/07/2025</t>
+  </si>
+  <si>
+    <t>9471674500</t>
   </si>
   <si>
     <t>UNIÃO APONTAMENTO ACABAMANTO E MOLDAGEM</t>
@@ -183,16 +195,19 @@
     <t>27/06/2025</t>
   </si>
   <si>
+    <t>26/07/2025</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
-    <t>32822</t>
+    <t>9571845086</t>
   </si>
   <si>
     <t>TRAVA ROTEIRO CPP</t>
   </si>
   <si>
-    <t>31314</t>
+    <t>9270747006</t>
   </si>
   <si>
     <t>Solicitação de Exportação de Planilha – Modelos e Centros de Usinagem</t>
@@ -207,19 +222,25 @@
     <t>Maio</t>
   </si>
   <si>
-    <t>32789</t>
+    <t>9572016309</t>
   </si>
   <si>
     <t>Bloco K - Envio dos dados do cálculo do custos para base de dados</t>
   </si>
   <si>
+    <t>9572701388</t>
+  </si>
+  <si>
     <t>Registro de Pintura - Registro Pintura</t>
   </si>
   <si>
+    <t>9572696366</t>
+  </si>
+  <si>
     <t>Procedimento de pintura - Registro Pintura</t>
   </si>
   <si>
-    <t>31511</t>
+    <t>9480911838</t>
   </si>
   <si>
     <t>Atualizar códigos de paradas UPR - Analisar</t>
@@ -228,7 +249,7 @@
     <t>30/06/2025</t>
   </si>
   <si>
-    <t>32845</t>
+    <t>9571807285</t>
   </si>
   <si>
     <t>Correção</t>
@@ -237,9 +258,15 @@
     <t>Correção | Relatório de Custos por Período</t>
   </si>
   <si>
+    <t>22/07/2025</t>
+  </si>
+  <si>
     <t>30069</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Solicitação de serviço</t>
   </si>
   <si>
@@ -255,22 +282,25 @@
     <t>ADH</t>
   </si>
   <si>
+    <t>16/07/2025</t>
+  </si>
+  <si>
     <t>Implantação</t>
   </si>
   <si>
-    <t>31233</t>
+    <t>9581038165</t>
   </si>
   <si>
     <t>Integração faturamento x Benner  Reunião de entrega</t>
   </si>
   <si>
-    <t>32723</t>
+    <t>9572308208</t>
   </si>
   <si>
     <t>Viabilidade e Proposta - Retificação de SPED Fiscal</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>9572908297</t>
   </si>
   <si>
     <t>Novo Sistema</t>
@@ -279,28 +309,34 @@
     <t>Flexibilizar a edição do horario na tela do agendamento</t>
   </si>
   <si>
-    <t>32843</t>
+    <t>21/07/2025</t>
+  </si>
+  <si>
+    <t>9571828796</t>
   </si>
   <si>
     <t>Habilitação Sistema de corridas</t>
   </si>
   <si>
-    <t>32387</t>
+    <t>9581444756</t>
   </si>
   <si>
     <t>Desenvolvimento de gráfico - aplicação Refugo Qlik Sense - Homologação</t>
   </si>
   <si>
+    <t>23/07/2025</t>
+  </si>
+  <si>
     <t>Homologação</t>
   </si>
   <si>
-    <t>32350</t>
+    <t>9472026211</t>
   </si>
   <si>
     <t>Revisão ETF</t>
   </si>
   <si>
-    <t>23839</t>
+    <t>9311733020</t>
   </si>
   <si>
     <t>Sistema de Separação Part 1/2</t>
@@ -312,40 +348,43 @@
     <t>Impedimento</t>
   </si>
   <si>
-    <t>32759</t>
+    <t>9572177894</t>
   </si>
   <si>
     <t>Paradas no BI</t>
   </si>
   <si>
-    <t>32144</t>
+    <t>9480965730</t>
   </si>
   <si>
     <t>Sistema de Radiografia automática em amostras</t>
   </si>
   <si>
+    <t>9572903585</t>
+  </si>
+  <si>
     <t>Prever/permitir sobreposição de horário na coleta</t>
   </si>
   <si>
-    <t>31794</t>
+    <t>9584040311</t>
   </si>
   <si>
     <t>Inclusão de romaneios manualmente no Recibo de Embarque</t>
   </si>
   <si>
-    <t>32816</t>
+    <t>9571906491</t>
   </si>
   <si>
     <t>Solicitação de alteração sistema de corridas</t>
   </si>
   <si>
-    <t>32821</t>
+    <t>9571864615</t>
   </si>
   <si>
     <t>Alteração Sist. Embalagem</t>
   </si>
   <si>
-    <t>32682</t>
+    <t>9572395273</t>
   </si>
   <si>
     <t>Data de entrada de documentos</t>
@@ -357,247 +396,265 @@
     <t>Apontamento Quebra de Canal - Homologação</t>
   </si>
   <si>
-    <t>31836</t>
+    <t>9581037909</t>
   </si>
   <si>
     <t>Melhoria WMS - Conferencia e Carregamento</t>
   </si>
   <si>
-    <t>32022</t>
+    <t>9581093504</t>
   </si>
   <si>
     <t>Apontamento Células de rebarbação automatizadas (Dalca e Lianco)</t>
   </si>
   <si>
-    <t>Boa tarde! Abrindo chamado referente ao desenvolvimento do sistema de apontamentos via CLP das células de rebarbação automatizadas. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Leonardo Barbosa de Moraes</t>
+    <t>20/07/2025</t>
+  </si>
+  <si>
+    <t>9581862710</t>
+  </si>
+  <si>
+    <t>Retrabalho da moldagem - Marcar Sequencia</t>
+  </si>
+  <si>
+    <t>9581079408</t>
+  </si>
+  <si>
+    <t>Mapeamento Digital</t>
+  </si>
+  <si>
+    <t>9571978776</t>
+  </si>
+  <si>
+    <t>Protocolo de entrega de teste do equipamento</t>
+  </si>
+  <si>
+    <t>9581068258</t>
+  </si>
+  <si>
+    <t>Planejamento de capacidade MOxdemanda de preventivas no sistema de manutenção (copy)</t>
+  </si>
+  <si>
+    <t>9572355386</t>
+  </si>
+  <si>
+    <t>Qlik - Tempo de Processamento</t>
+  </si>
+  <si>
+    <t>9581114741</t>
+  </si>
+  <si>
+    <t>Apontamento eletrônico corte pó de ferro  - Homologação</t>
+  </si>
+  <si>
+    <t>29848</t>
+  </si>
+  <si>
+    <t>Alteração da referencia de Etiqueta para Romaneio</t>
+  </si>
+  <si>
+    <t>Boa tarde Precisamos que seja realizada a alteração do sistema abaixo onde faz a busca das etiquetas amarelas para os romaneios "ATIVO", desconsiderando o BOX 0. Deve aparecer disponível para vincular no ticket todos os romaneios do modelo/conjunto conforme as regras atuais do sistema. Também deve s</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>9572365628</t>
+  </si>
+  <si>
+    <t>Qlik - Vinculação de Atualização Aplic. Expedição</t>
+  </si>
+  <si>
+    <t>9572372225</t>
+  </si>
+  <si>
+    <t>Qlik - Vinculo de Atualização Comparação de volume</t>
+  </si>
+  <si>
+    <t>9374595435</t>
+  </si>
+  <si>
+    <t>Projeto Fluxo - Inclusão de coluna com informação de conclusão de toto (s/n)</t>
+  </si>
+  <si>
+    <t>13/06/2025</t>
+  </si>
+  <si>
+    <t>9581294400</t>
+  </si>
+  <si>
+    <t>Conversão KB TOTO</t>
+  </si>
+  <si>
+    <t>9581130427</t>
+  </si>
+  <si>
+    <t>Retrabalho da moldagem - Classificação</t>
+  </si>
+  <si>
+    <t>9572917863</t>
+  </si>
+  <si>
+    <t>Criar campo para informar se o tipo de agendamento é um "Encaixe"</t>
+  </si>
+  <si>
+    <t>9581120435</t>
+  </si>
+  <si>
+    <t>Planilha - Controle de OSs - Instalação Industrial - Homologação</t>
+  </si>
+  <si>
+    <t>9571697835</t>
+  </si>
+  <si>
+    <t>ALTERAÇÃO VENCIMENTO VOLVO DO BRASIL</t>
+  </si>
+  <si>
+    <t>9572913497</t>
+  </si>
+  <si>
+    <t>Criar um novo status denominado 'carregado'</t>
+  </si>
+  <si>
+    <t>9279941478</t>
+  </si>
+  <si>
+    <t>Planilhão via Qlik sense (copy)</t>
+  </si>
+  <si>
+    <t>9572540611</t>
+  </si>
+  <si>
+    <t>Baixa de Estoque de Embalagem Expedição</t>
+  </si>
+  <si>
+    <t>9572919651</t>
+  </si>
+  <si>
+    <t>Desenvolver alternativa para enviar um link para o cliente escolher data e hora do agendamento</t>
+  </si>
+  <si>
+    <t>9572047141</t>
+  </si>
+  <si>
+    <t>Ações reunião sobre app da USE</t>
+  </si>
+  <si>
+    <t>9571708282</t>
+  </si>
+  <si>
+    <t>[NIMBI] API's para a integração de requisição gerado no ERP &gt; Nimbi</t>
+  </si>
+  <si>
+    <t>9572414699</t>
+  </si>
+  <si>
+    <t>Inclusão de Campo para Consulta de Dados de Materiais</t>
+  </si>
+  <si>
+    <t>9373265697</t>
+  </si>
+  <si>
+    <t>ACRESENTAR BOTÃO PARA RELATORIO DE ALTERAÇÕES DE APONTMAENTOS ELETRONICOS</t>
+  </si>
+  <si>
+    <t>9571986410</t>
+  </si>
+  <si>
+    <t>Alteração descrição item da FTF 110129 - Holtec</t>
+  </si>
+  <si>
+    <t>18098513321</t>
+  </si>
+  <si>
+    <t>ACRESENTAR BOTÃO PARA RELATORIO DE ALTERAÇÕES DE APONTMAENTOS ELETRONICOS (copy)</t>
+  </si>
+  <si>
+    <t>02/10/2025</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t>9572423879</t>
+  </si>
+  <si>
+    <t>ALTERAÇÃO CAMPO SISTEMA INVOICES</t>
+  </si>
+  <si>
+    <t>9581425919</t>
+  </si>
+  <si>
+    <t>Aplicação de controle de consumo e custo de PROEX e Antecipação de Caterpillar - Reunião (copy)</t>
+  </si>
+  <si>
+    <t>9382249294</t>
+  </si>
+  <si>
+    <t>ALERTA DE REVISÃO X BLOQUEIO DE MODELO</t>
+  </si>
+  <si>
+    <t>16/06/2025</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>9572065560</t>
+  </si>
+  <si>
+    <t>Usuário abertura OM - WMS</t>
+  </si>
+  <si>
+    <t>30012</t>
+  </si>
+  <si>
+    <t>PCP</t>
+  </si>
+  <si>
+    <t>Saneamento de dados para APS</t>
+  </si>
+  <si>
+    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
+  </si>
+  <si>
+    <t>João Pedro Beccon</t>
   </si>
   <si>
     <t>Sistemas</t>
   </si>
   <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>32310</t>
-  </si>
-  <si>
-    <t>Retrabalho da moldagem - Marcar Sequencia</t>
-  </si>
-  <si>
-    <t>32298</t>
-  </si>
-  <si>
-    <t>Mapeamento Digital</t>
-  </si>
-  <si>
-    <t>32800</t>
-  </si>
-  <si>
-    <t>Protocolo de entrega de teste do equipamento</t>
-  </si>
-  <si>
-    <t>32363</t>
-  </si>
-  <si>
-    <t>Planejamento de capacidade MOxdemanda de preventivas no sistema de manutenção (copy)</t>
-  </si>
-  <si>
-    <t>32687</t>
-  </si>
-  <si>
-    <t>Qlik - Tempo de Processamento</t>
-  </si>
-  <si>
-    <t>31292</t>
-  </si>
-  <si>
-    <t>Apontamento eletrônico corte pó de ferro  - Homologação</t>
-  </si>
-  <si>
-    <t>29848</t>
-  </si>
-  <si>
-    <t>Alteração da referencia de Etiqueta para Romaneio</t>
-  </si>
-  <si>
-    <t>Boa tarde Precisamos que seja realizada a alteração do sistema abaixo onde faz a busca das etiquetas amarelas para os romaneios "ATIVO", desconsiderando o BOX 0. Deve aparecer disponível para vincular no ticket todos os romaneios do modelo/conjunto conforme as regras atuais do sistema. Também deve s</t>
-  </si>
-  <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
-    <t>32686</t>
-  </si>
-  <si>
-    <t>Qlik - Vinculação de Atualização Aplic. Expedição</t>
-  </si>
-  <si>
-    <t>32685</t>
-  </si>
-  <si>
-    <t>Qlik - Vinculo de Atualização Comparação de volume</t>
-  </si>
-  <si>
-    <t>32120</t>
-  </si>
-  <si>
-    <t>Projeto Fluxo - Inclusão de coluna com informação de conclusão de toto (s/n)</t>
-  </si>
-  <si>
-    <t>13/06/2025</t>
-  </si>
-  <si>
-    <t>31015</t>
-  </si>
-  <si>
-    <t>Conversão KB TOTO</t>
-  </si>
-  <si>
-    <t>Retrabalho da moldagem - Classificação</t>
-  </si>
-  <si>
-    <t>Criar campo para informar se o tipo de agendamento é um "Encaixe"</t>
-  </si>
-  <si>
-    <t>32113</t>
-  </si>
-  <si>
-    <t>Planilha - Controle de OSs - Instalação Industrial - Homologação</t>
-  </si>
-  <si>
-    <t>32849</t>
-  </si>
-  <si>
-    <t>ALTERAÇÃO VENCIMENTO VOLVO DO BRASIL</t>
-  </si>
-  <si>
-    <t>Criar um novo status denominado 'carregado'</t>
-  </si>
-  <si>
-    <t>31685</t>
-  </si>
-  <si>
-    <t>Planilhão via Qlik sense (copy)</t>
-  </si>
-  <si>
-    <t>32588</t>
-  </si>
-  <si>
-    <t>Baixa de Estoque de Embalagem Expedição</t>
-  </si>
-  <si>
-    <t>Desenvolver alternativa para enviar um link para o cliente escolher data e hora do agendamento</t>
-  </si>
-  <si>
-    <t>32786</t>
-  </si>
-  <si>
-    <t>Ações reunião sobre app da USE</t>
-  </si>
-  <si>
-    <t>32848</t>
-  </si>
-  <si>
-    <t>[NIMBI] API's para a integração de requisição gerado no ERP &gt; Nimbi</t>
-  </si>
-  <si>
-    <t>32674</t>
-  </si>
-  <si>
-    <t>Inclusão de Campo para Consulta de Dados de Materiais</t>
-  </si>
-  <si>
-    <t>32149</t>
-  </si>
-  <si>
-    <t>ACRESENTAR BOTÃO PARA RELATORIO DE ALTERAÇÕES DE APONTMAENTOS ELETRONICOS</t>
-  </si>
-  <si>
-    <t>32795</t>
-  </si>
-  <si>
-    <t>Alteração descrição item da FTF 110129 - Holtec</t>
-  </si>
-  <si>
-    <t>ACRESENTAR BOTÃO PARA RELATORIO DE ALTERAÇÕES DE APONTMAENTOS ELETRONICOS (copy)</t>
-  </si>
-  <si>
-    <t>02/10/2025</t>
-  </si>
-  <si>
-    <t>Outubro</t>
-  </si>
-  <si>
-    <t>32669</t>
-  </si>
-  <si>
-    <t>ALTERAÇÃO CAMPO SISTEMA INVOICES</t>
-  </si>
-  <si>
-    <t>32287</t>
-  </si>
-  <si>
-    <t>Aplicação de controle de consumo e custo de PROEX e Antecipação de Caterpillar - Reunião (copy)</t>
-  </si>
-  <si>
-    <t>31609</t>
-  </si>
-  <si>
-    <t>ALERTA DE REVISÃO X BLOQUEIO DE MODELO</t>
-  </si>
-  <si>
-    <t>16/06/2025</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>32782</t>
-  </si>
-  <si>
-    <t>Usuário abertura OM - WMS</t>
-  </si>
-  <si>
-    <t>30012</t>
-  </si>
-  <si>
-    <t>Saneamento de dados para APS</t>
-  </si>
-  <si>
-    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
-  </si>
-  <si>
-    <t>João Pedro Beccon</t>
-  </si>
-  <si>
-    <t>32485</t>
+    <t>9581342540</t>
   </si>
   <si>
     <t>Tempos dos modelos UPR</t>
   </si>
   <si>
-    <t>32402</t>
+    <t>9572627780</t>
   </si>
   <si>
     <t>Relatório do Funil de Vendas - 80%</t>
   </si>
   <si>
-    <t>32777</t>
+    <t>9572090591</t>
   </si>
   <si>
     <t>CFOP notas de remessa - ERP Altona</t>
   </si>
   <si>
+    <t>9572923286</t>
+  </si>
+  <si>
     <t>Analisar o agendamento recorrente (cliente volvo e caterpillar</t>
   </si>
   <si>
+    <t>9572925652</t>
+  </si>
+  <si>
     <t>Criar calendário/visão para o agendamento da remessa e retorno de industrialização</t>
   </si>
   <si>
-    <t>26571</t>
+    <t>9374955877</t>
   </si>
   <si>
     <t>Retirar de peças do deposito para versão WMS</t>
@@ -615,7 +672,7 @@
     <t>02/06/2026</t>
   </si>
   <si>
-    <t>32768</t>
+    <t>9572121502</t>
   </si>
   <si>
     <t>SISTEMA INVOICE - IMPRESSÃO ETIQUETA - TRAVA NOTA FISCAL</t>
@@ -627,16 +684,19 @@
     <t>Divergência valores de vendas</t>
   </si>
   <si>
+    <t>9572930074</t>
+  </si>
+  <si>
     <t>No agendamento de remessa/retorno, criar campo para informar a transportadora</t>
   </si>
   <si>
-    <t>30905</t>
+    <t>9382249472</t>
   </si>
   <si>
     <t>ACVO - REUNIÃO</t>
   </si>
   <si>
-    <t>32763</t>
+    <t>9572158537</t>
   </si>
   <si>
     <t>Contas contábeis para notas de entrada de remessa quando for empresa do grupo</t>
@@ -651,19 +711,19 @@
     <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
   </si>
   <si>
-    <t>32041</t>
+    <t>9581037232</t>
   </si>
   <si>
     <t>Custos de Armazenagem/MP</t>
   </si>
   <si>
-    <t>32080</t>
+    <t>9581037377</t>
   </si>
   <si>
     <t>GRUPO DE RECURSOS PADRÃO</t>
   </si>
   <si>
-    <t>32348</t>
+    <t>9581037668</t>
   </si>
   <si>
     <t>Códigos dos materiais - Definição do Escopo</t>
@@ -678,58 +738,58 @@
     <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
   </si>
   <si>
-    <t>32333</t>
+    <t>9472060028</t>
   </si>
   <si>
     <t>Relatório Invoices x OTF x Modelo</t>
   </si>
   <si>
-    <t>26428</t>
+    <t>9481074683</t>
   </si>
   <si>
     <t>CONSULTA EMBARQUES ALTONA</t>
   </si>
   <si>
-    <t>32875</t>
+    <t>28/07/2025</t>
+  </si>
+  <si>
+    <t>9596082288</t>
   </si>
   <si>
     <t>Rateio Tempo Padrão</t>
   </si>
   <si>
-    <t>15/07/2025</t>
-  </si>
-  <si>
-    <t>32772</t>
+    <t>9572099509</t>
   </si>
   <si>
     <t>ACRESCENTAR MOTIVO DE PARADA "FALTA DE GAS NA REDE</t>
   </si>
   <si>
-    <t>32790</t>
+    <t>9572004910</t>
   </si>
   <si>
     <t>Alteração de rateio - IROG acabamento</t>
   </si>
   <si>
-    <t>32544</t>
+    <t>9471564542</t>
   </si>
   <si>
     <t>Aplicação IROG - Dados 3º Turno</t>
   </si>
   <si>
-    <t>32850</t>
+    <t>9571692064</t>
   </si>
   <si>
     <t>Criar código para Pendência de Moldagem na Aciaria</t>
   </si>
   <si>
-    <t>32536</t>
+    <t>9471607101</t>
   </si>
   <si>
     <t>DESENVOLVIMENTO DE CONTROLE DE DISPOSITIVOS DE USINAGEM</t>
   </si>
   <si>
-    <t>32510</t>
+    <t>9471684958</t>
   </si>
   <si>
     <t>Flag máquina crítica sim ou não</t>
@@ -744,7 +804,7 @@
     <t>Na geração das OP’s vincular as restrições as etapas de fabricação</t>
   </si>
   <si>
-    <t>32590</t>
+    <t>9572530301</t>
   </si>
   <si>
     <t>Radiografia para Amostras</t>
@@ -762,7 +822,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-15</t>
+    <t>Mai/2025</t>
   </si>
   <si>
     <t>Base</t>
@@ -1395,7 +1455,7 @@
         <v>33</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1442,13 +1502,13 @@
         <v>36</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>39</v>
@@ -1489,7 +1549,7 @@
         <v>23</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1506,7 +1566,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1518,10 +1578,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1536,7 +1596,7 @@
         <v>23</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1553,7 +1613,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1565,10 +1625,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1583,13 +1643,13 @@
         <v>33</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>27</v>
@@ -1600,7 +1660,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1612,10 +1672,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1630,13 +1690,13 @@
         <v>33</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -1647,7 +1707,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1659,10 +1719,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1694,7 +1754,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1706,10 +1766,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1724,7 +1784,7 @@
         <v>23</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1741,7 +1801,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1753,10 +1813,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1768,10 +1828,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1780,7 +1840,7 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>40</v>
@@ -1788,7 +1848,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1800,10 +1860,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1835,7 +1895,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1847,10 +1907,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1862,27 +1922,27 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1894,10 +1954,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1929,7 +1989,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1941,10 +2001,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1959,7 +2019,7 @@
         <v>23</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1976,7 +2036,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1988,10 +2048,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -2023,7 +2083,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -2035,10 +2095,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -2050,10 +2110,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -2062,7 +2122,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>40</v>
@@ -2070,22 +2130,22 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -2100,7 +2160,7 @@
         <v>23</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -2117,40 +2177,40 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>26</v>
@@ -2164,7 +2224,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -2176,10 +2236,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -2194,13 +2254,13 @@
         <v>33</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>27</v>
@@ -2211,7 +2271,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2223,10 +2283,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>32</v>
@@ -2241,7 +2301,7 @@
         <v>23</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -2258,22 +2318,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2288,7 +2348,7 @@
         <v>23</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2305,7 +2365,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2317,10 +2377,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2352,7 +2412,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2364,10 +2424,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2382,13 +2442,13 @@
         <v>33</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>27</v>
@@ -2399,7 +2459,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2411,10 +2471,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>32</v>
@@ -2426,7 +2486,7 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>24</v>
@@ -2438,7 +2498,7 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>40</v>
@@ -2446,7 +2506,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2458,10 +2518,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2473,16 +2533,16 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>39</v>
@@ -2493,7 +2553,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2505,10 +2565,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2523,13 +2583,13 @@
         <v>23</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>27</v>
@@ -2540,7 +2600,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2552,10 +2612,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2567,19 +2627,19 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>40</v>
@@ -2587,22 +2647,22 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2617,7 +2677,7 @@
         <v>23</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2634,7 +2694,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2646,10 +2706,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2664,13 +2724,13 @@
         <v>33</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>27</v>
@@ -2681,7 +2741,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2693,10 +2753,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2728,7 +2788,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2740,10 +2800,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2758,7 +2818,7 @@
         <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2775,7 +2835,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2787,10 +2847,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2805,7 +2865,7 @@
         <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2822,7 +2882,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2834,10 +2894,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2852,7 +2912,7 @@
         <v>33</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2869,7 +2929,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2881,10 +2941,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2899,13 +2959,13 @@
         <v>33</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>27</v>
@@ -2916,7 +2976,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2925,28 +2985,28 @@
         <v>17</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2963,7 +3023,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2975,10 +3035,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2993,7 +3053,7 @@
         <v>33</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -3010,7 +3070,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -3022,10 +3082,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>32</v>
@@ -3040,7 +3100,7 @@
         <v>33</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -3057,7 +3117,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -3069,10 +3129,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -3087,7 +3147,7 @@
         <v>23</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -3104,7 +3164,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -3116,10 +3176,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -3134,13 +3194,13 @@
         <v>33</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>27</v>
@@ -3151,7 +3211,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -3163,10 +3223,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -3198,7 +3258,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -3210,10 +3270,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -3228,7 +3288,7 @@
         <v>33</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -3245,43 +3305,43 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>27</v>
@@ -3292,7 +3352,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3304,10 +3364,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3322,7 +3382,7 @@
         <v>23</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3339,7 +3399,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3351,10 +3411,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3369,7 +3429,7 @@
         <v>23</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3386,7 +3446,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3398,10 +3458,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3413,10 +3473,10 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3433,7 +3493,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3445,10 +3505,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3463,7 +3523,7 @@
         <v>33</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3480,7 +3540,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3492,10 +3552,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3510,13 +3570,13 @@
         <v>33</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>27</v>
@@ -3527,22 +3587,22 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>85</v>
+        <v>159</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3557,7 +3617,7 @@
         <v>23</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -3574,7 +3634,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3586,10 +3646,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3604,7 +3664,7 @@
         <v>33</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3621,7 +3681,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3633,10 +3693,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3651,13 +3711,13 @@
         <v>23</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>27</v>
@@ -3668,22 +3728,22 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3698,7 +3758,7 @@
         <v>23</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -3715,7 +3775,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3727,10 +3787,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3745,13 +3805,13 @@
         <v>36</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>39</v>
@@ -3762,7 +3822,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3774,10 +3834,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
@@ -3792,13 +3852,13 @@
         <v>23</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>27</v>
@@ -3809,22 +3869,22 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3839,7 +3899,7 @@
         <v>23</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>25</v>
@@ -3856,7 +3916,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3868,10 +3928,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3886,7 +3946,7 @@
         <v>23</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>25</v>
@@ -3903,7 +3963,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3915,10 +3975,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -3933,7 +3993,7 @@
         <v>23</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>25</v>
@@ -3950,7 +4010,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -3962,10 +4022,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
@@ -3980,7 +4040,7 @@
         <v>23</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>25</v>
@@ -3997,7 +4057,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
@@ -4009,10 +4069,10 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
@@ -4024,10 +4084,10 @@
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>25</v>
@@ -4044,7 +4104,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -4056,10 +4116,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -4074,7 +4134,7 @@
         <v>23</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>25</v>
@@ -4091,7 +4151,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
@@ -4103,10 +4163,10 @@
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
@@ -4118,10 +4178,10 @@
         <v>22</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>25</v>
@@ -4133,12 +4193,12 @@
         <v>39</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
@@ -4150,10 +4210,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
@@ -4168,7 +4228,7 @@
         <v>23</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>25</v>
@@ -4185,7 +4245,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
@@ -4197,10 +4257,10 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
@@ -4215,13 +4275,13 @@
         <v>33</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>27</v>
@@ -4232,7 +4292,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -4244,10 +4304,10 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>20</v>
@@ -4259,19 +4319,19 @@
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>40</v>
@@ -4279,7 +4339,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
@@ -4291,10 +4351,10 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>20</v>
@@ -4309,7 +4369,7 @@
         <v>23</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>25</v>
@@ -4326,37 +4386,37 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>25</v>
@@ -4373,7 +4433,7 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
@@ -4385,10 +4445,10 @@
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>32</v>
@@ -4403,7 +4463,7 @@
         <v>33</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>25</v>
@@ -4420,7 +4480,7 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
@@ -4432,10 +4492,10 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
@@ -4450,7 +4510,7 @@
         <v>23</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>25</v>
@@ -4467,7 +4527,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
@@ -4479,10 +4539,10 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
@@ -4497,7 +4557,7 @@
         <v>23</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>25</v>
@@ -4514,22 +4574,22 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>85</v>
+        <v>209</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>20</v>
@@ -4544,7 +4604,7 @@
         <v>23</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>25</v>
@@ -4561,22 +4621,22 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>85</v>
+        <v>211</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>20</v>
@@ -4591,7 +4651,7 @@
         <v>23</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>25</v>
@@ -4608,7 +4668,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
@@ -4620,10 +4680,10 @@
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>20</v>
@@ -4635,16 +4695,16 @@
         <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>27</v>
@@ -4655,37 +4715,37 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>25</v>
@@ -4702,7 +4762,7 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>16</v>
@@ -4714,10 +4774,10 @@
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
@@ -4732,7 +4792,7 @@
         <v>23</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>25</v>
@@ -4749,22 +4809,22 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>32</v>
@@ -4779,7 +4839,7 @@
         <v>33</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>25</v>
@@ -4796,22 +4856,22 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>85</v>
+        <v>223</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>20</v>
@@ -4826,7 +4886,7 @@
         <v>23</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>25</v>
@@ -4843,7 +4903,7 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>16</v>
@@ -4855,10 +4915,10 @@
         <v>18</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>20</v>
@@ -4870,19 +4930,19 @@
         <v>22</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="O77" s="2" t="s">
         <v>40</v>
@@ -4890,7 +4950,7 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
@@ -4902,10 +4962,10 @@
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
@@ -4920,7 +4980,7 @@
         <v>23</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>25</v>
@@ -4937,43 +4997,43 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N79" s="2" t="s">
         <v>27</v>
@@ -4984,7 +5044,7 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>16</v>
@@ -4996,10 +5056,10 @@
         <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>32</v>
@@ -5014,13 +5074,13 @@
         <v>33</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>27</v>
@@ -5031,7 +5091,7 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>16</v>
@@ -5043,10 +5103,10 @@
         <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
@@ -5061,10 +5121,10 @@
         <v>33</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M81" s="2" t="s">
         <v>26</v>
@@ -5078,7 +5138,7 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>16</v>
@@ -5090,10 +5150,10 @@
         <v>18</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>32</v>
@@ -5108,13 +5168,13 @@
         <v>33</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>27</v>
@@ -5125,43 +5185,43 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N83" s="2" t="s">
         <v>27</v>
@@ -5172,7 +5232,7 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>16</v>
@@ -5184,10 +5244,10 @@
         <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>20</v>
@@ -5199,7 +5259,7 @@
         <v>22</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>24</v>
@@ -5211,7 +5271,7 @@
         <v>26</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O84" s="2" t="s">
         <v>40</v>
@@ -5219,7 +5279,7 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>16</v>
@@ -5231,10 +5291,10 @@
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>20</v>
@@ -5246,19 +5306,19 @@
         <v>22</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>24</v>
+        <v>245</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="O85" s="2" t="s">
         <v>40</v>
@@ -5266,22 +5326,22 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>20</v>
@@ -5293,7 +5353,7 @@
         <v>22</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>227</v>
+        <v>24</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>24</v>
@@ -5305,7 +5365,7 @@
         <v>26</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="O86" s="2" t="s">
         <v>28</v>
@@ -5313,7 +5373,7 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>16</v>
@@ -5325,10 +5385,10 @@
         <v>18</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>20</v>
@@ -5343,7 +5403,7 @@
         <v>23</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>25</v>
@@ -5360,7 +5420,7 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>16</v>
@@ -5372,10 +5432,10 @@
         <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>32</v>
@@ -5390,7 +5450,7 @@
         <v>23</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L88" s="2" t="s">
         <v>25</v>
@@ -5407,22 +5467,22 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>20</v>
@@ -5434,10 +5494,10 @@
         <v>22</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>25</v>
@@ -5446,7 +5506,7 @@
         <v>26</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O89" s="2" t="s">
         <v>40</v>
@@ -5454,7 +5514,7 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>16</v>
@@ -5466,10 +5526,10 @@
         <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>20</v>
@@ -5484,7 +5544,7 @@
         <v>23</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>25</v>
@@ -5501,7 +5561,7 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>16</v>
@@ -5513,10 +5573,10 @@
         <v>18</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>20</v>
@@ -5528,10 +5588,10 @@
         <v>22</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>25</v>
@@ -5540,7 +5600,7 @@
         <v>26</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O91" s="2" t="s">
         <v>40</v>
@@ -5548,7 +5608,7 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>16</v>
@@ -5560,10 +5620,10 @@
         <v>18</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>32</v>
@@ -5575,10 +5635,10 @@
         <v>22</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>25</v>
@@ -5587,7 +5647,7 @@
         <v>26</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O92" s="2" t="s">
         <v>40</v>
@@ -5595,40 +5655,40 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M93" s="2" t="s">
         <v>26</v>
@@ -5642,37 +5702,37 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>25</v>
@@ -5689,7 +5749,7 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>16</v>
@@ -5701,10 +5761,10 @@
         <v>18</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>20</v>
@@ -5719,10 +5779,10 @@
         <v>23</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M95" s="2" t="s">
         <v>26</v>
@@ -5736,37 +5796,37 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>25</v>
@@ -5783,40 +5843,40 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M97" s="2" t="s">
         <v>26</v>
@@ -5841,23 +5901,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="D2" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5865,16 +5925,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5885,15 +5945,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>303.57</v>
+        <v>36.51</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5906,7 +5966,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K23">
         <v>6</v>
@@ -5914,7 +5974,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5945,12 +6005,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="B2">
         <v>96</v>
@@ -5964,35 +6024,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>303.57</v>
+        <v>36.51</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -6000,7 +6060,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -6009,13 +6069,13 @@
         <v>77</v>
       </c>
       <c r="G10" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -6030,12 +6090,18 @@
         <v>39</v>
       </c>
       <c r="Q10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E11">
         <v>8</v>
@@ -6050,10 +6116,10 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="M11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N11">
         <v>16</v>
@@ -6062,10 +6128,16 @@
         <v>27</v>
       </c>
       <c r="Q11">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
       <c r="D12" t="s">
         <v>30</v>
       </c>
@@ -6079,73 +6151,67 @@
         <v>79</v>
       </c>
       <c r="J12" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="K12">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="N12">
         <v>3</v>
       </c>
       <c r="P12" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="Q12">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E13">
         <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N13">
         <v>4</v>
       </c>
       <c r="P13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Q13">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N14">
         <v>6</v>
       </c>
-      <c r="P14" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q14">
-        <v>2</v>
-      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="N15">
         <v>2</v>
@@ -6153,7 +6219,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -6161,7 +6227,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -6169,10 +6235,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -6180,7 +6246,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -6188,142 +6254,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>196</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>309</v>
+        <v>369</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>197</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>298</v>
+        <v>369</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>240</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>182</v>
+        <v>50</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>298</v>
+        <v>369</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>242</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>182</v>
+        <v>64</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>298</v>
+        <v>369</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>245</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>298</v>
+        <v>369</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>246</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>182</v>
+        <v>101</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>295</v>
+        <v>369</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>183</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>224</v>
+        <v>369</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>19</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
